--- a/excel/pacifico-dex-sociedad-anonima-cerrada_ccc.xlsx
+++ b/excel/pacifico-dex-sociedad-anonima-cerrada_ccc.xlsx
@@ -609,7 +609,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>25384</v>
+        <v>96411</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -643,12 +643,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>C001489520</t>
+          <t>C001752251</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>C001489520 - LUJAN CUAREZ CARLOS VIDAL</t>
+          <t>C001752251 - INJANTE DE LA CRUZ MIRELLA DEL ROSARIO.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -672,7 +672,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>S17844114</t>
+          <t>S17848138</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -725,7 +725,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>18216</v>
+        <v>67358</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -759,12 +759,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>C001330256</t>
+          <t>C004060670</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>C001330256 - GUTIERREZ SANTARIA NATALIA</t>
+          <t>C004060670 - CARRASCAL PEVE MELISSA JACKELINE</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>S17850095</t>
+          <t>S17843850</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -957,7 +957,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>96411</v>
+        <v>25384</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -991,12 +991,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>C001752251</t>
+          <t>C001489520</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>C001752251 - INJANTE DE LA CRUZ MIRELLA DEL ROSARIO.</t>
+          <t>C001489520 - LUJAN CUAREZ CARLOS VIDAL</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>S17848138</t>
+          <t>S17844114</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1073,7 +1073,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>67358</v>
+        <v>18216</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1107,12 +1107,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>C004060670</t>
+          <t>C001330256</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>C004060670 - CARRASCAL PEVE MELISSA JACKELINE</t>
+          <t>C001330256 - GUTIERREZ SANTARIA NATALIA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>S17843850</t>
+          <t>S17850095</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1189,7 +1189,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>70712</v>
+        <v>3722</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1223,12 +1223,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>C004042768</t>
+          <t>C000872160</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>C004042768 - ACHAMISO ARONI ESTEFANY MARIBEL</t>
+          <t>C000872160 - QUISPE ABURTO GABY VICTORIA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>S17799639</t>
+          <t>S17812733</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1283,7 +1283,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr"/>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr">
@@ -1421,7 +1425,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>3722</v>
+        <v>70712</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1455,12 +1459,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>C000872160</t>
+          <t>C004042768</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>C000872160 - QUISPE ABURTO GABY VICTORIA</t>
+          <t>C004042768 - ACHAMISO ARONI ESTEFANY MARIBEL</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1484,7 +1488,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>S17812733</t>
+          <t>S17799639</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1507,7 +1511,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1515,11 +1519,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
+      <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr">
@@ -1541,7 +1541,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>4284</v>
+        <v>108113</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1575,12 +1575,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>C000881938</t>
+          <t>C004240818</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>C000881938 - MONTOYA CARRIZALES ROSA</t>
+          <t>C004240818 - DONAYRE PACHECO GAUDY VALERIA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1600,11 +1600,11 @@
         <v>46235</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>S17779454</t>
+          <t>S17861375</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1650,14 +1650,14 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>10381</v>
+        <v>107524</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1691,12 +1691,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>C000881361</t>
+          <t>C000875697</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>C000881361 - CONISLLA FLORES BLANCA MARLENY</t>
+          <t>C000875697 - PIZARRO MANTARI MARIA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>S17774204</t>
+          <t>S17772414</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1766,14 +1766,14 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>108113</v>
+        <v>4284</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1807,12 +1807,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>C004240818</t>
+          <t>C000881938</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>C004240818 - DONAYRE PACHECO GAUDY VALERIA</t>
+          <t>C000881938 - MONTOYA CARRIZALES ROSA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1832,11 +1832,11 @@
         <v>46235</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>46247</v>
+        <v>46245</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>S17861375</t>
+          <t>S17779454</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1882,14 +1882,14 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>107524</v>
+        <v>10381</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1923,12 +1923,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>C000875697</t>
+          <t>C000881361</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>C000875697 - PIZARRO MANTARI MARIA</t>
+          <t>C000881361 - CONISLLA FLORES BLANCA MARLENY</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>S17772414</t>
+          <t>S17774204</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1998,14 +1998,14 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>78515</v>
+        <v>25681</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -2039,12 +2039,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>C004192518</t>
+          <t>C001492706</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>C004192518 - LEON HERNANDEZ KIHARA RUBY</t>
+          <t>C001492706 - ASTO AYJA ESTHER ELIZABETH</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2064,11 +2064,11 @@
         <v>46235</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>46245</v>
+        <v>46244</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>S17779221</t>
+          <t>S17752334</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2091,7 +2091,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2121,7 +2121,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>87686</v>
+        <v>7490</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -2155,12 +2155,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>C001481930</t>
+          <t>C000875833</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>C001481930 - FARFAN QUIROZ NARDA UCELLY</t>
+          <t>C000875833 - ARROYO BENDEZU EDDY LUZ</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2180,11 +2180,11 @@
         <v>46235</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>46245</v>
+        <v>46244</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>S17788110</t>
+          <t>S17744795</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2237,7 +2237,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>101178</v>
+        <v>5176</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -2271,12 +2271,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>C004142350</t>
+          <t>C000877077</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>C004142350 - LARA GAVILAN JUAN ROMARIO</t>
+          <t>C000877077 - HUAMAN HUAMANI ISABEL</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2296,11 +2296,11 @@
         <v>46235</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>46247</v>
+        <v>46244</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>S17842944</t>
+          <t>S17751235</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2353,7 +2353,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>96413</v>
+        <v>34051</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -2387,12 +2387,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>C001572913</t>
+          <t>C001612448</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>C001572913 - CCAYCO CANALES MARISA</t>
+          <t>C001612448 - HERNANDEZ SOTO PATRICIA ROSA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2412,11 +2412,11 @@
         <v>46235</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>S17753586</t>
+          <t>S17777792</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2469,7 +2469,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>95021</v>
+        <v>64114</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -2503,12 +2503,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>C001360879</t>
+          <t>C001725109</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>C001360879 - OYOLO LLAMOCCA FAUSTA DELIA</t>
+          <t>C001725109 - ORE CHUNG MARIA ESTHER</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>S17750296</t>
+          <t>S17748633</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2555,7 +2555,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2585,7 +2585,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>34051</v>
+        <v>78515</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -2619,12 +2619,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>C001612448</t>
+          <t>C004192518</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>C001612448 - HERNANDEZ SOTO PATRICIA ROSA</t>
+          <t>C004192518 - LEON HERNANDEZ KIHARA RUBY</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>S17777792</t>
+          <t>S17779221</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2701,7 +2701,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>64114</v>
+        <v>87686</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -2735,12 +2735,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>C001725109</t>
+          <t>C001481930</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>C001725109 - ORE CHUNG MARIA ESTHER</t>
+          <t>C001481930 - FARFAN QUIROZ NARDA UCELLY</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2760,11 +2760,11 @@
         <v>46235</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>S17748633</t>
+          <t>S17788110</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2817,7 +2817,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>25681</v>
+        <v>101178</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -2851,12 +2851,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>C001492706</t>
+          <t>C004142350</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>C001492706 - ASTO AYJA ESTHER ELIZABETH</t>
+          <t>C004142350 - LARA GAVILAN JUAN ROMARIO</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2876,11 +2876,11 @@
         <v>46235</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>S17752334</t>
+          <t>S17842944</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2903,7 +2903,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2933,7 +2933,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>7490</v>
+        <v>95021</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -2967,12 +2967,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>C000875833</t>
+          <t>C001360879</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>C000875833 - ARROYO BENDEZU EDDY LUZ</t>
+          <t>C001360879 - OYOLO LLAMOCCA FAUSTA DELIA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>S17744795</t>
+          <t>S17750296</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -3049,7 +3049,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>5176</v>
+        <v>96413</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -3083,12 +3083,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>C000877077</t>
+          <t>C001572913</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>C000877077 - HUAMAN HUAMANI ISABEL</t>
+          <t>C001572913 - CCAYCO CANALES MARISA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>S17751235</t>
+          <t>S17753586</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -3165,7 +3165,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>3696</v>
+        <v>92572</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -3199,12 +3199,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>C000875691</t>
+          <t>C004209286</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>C000875691 - PUJAICO RUIZ DE FERNANDEZ ANGELA</t>
+          <t>C004209286 - ORMEÑO HERNANDEZ MARCOS JAVIER</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>S17742299</t>
+          <t>S17736445</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3281,7 +3281,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>12277</v>
+        <v>80410</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -3315,12 +3315,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>C001161300</t>
+          <t>C004218242</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>C001161300 - RIVERA GOMEZ ANGEL RENE</t>
+          <t>C004218242 - JHONG RAFFO CRISTIABEL</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3340,11 +3340,11 @@
         <v>46235</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>46242</v>
+        <v>46247</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>S17724116</t>
+          <t>S17838631</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3397,7 +3397,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>31604</v>
+        <v>69615</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -3431,12 +3431,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>C001538483</t>
+          <t>C001761926</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>C001538483 - DE LA ROSA AZURZA REYNA</t>
+          <t>C001761926 - ESPINOZA CHOQUE SUSANA ARACELI</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3456,11 +3456,11 @@
         <v>46235</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>46244</v>
+        <v>46242</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>S17740567</t>
+          <t>S17725411</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3745,7 +3745,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>92572</v>
+        <v>3696</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -3779,12 +3779,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>C004209286</t>
+          <t>C000875691</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>C004209286 - ORMEÑO HERNANDEZ MARCOS JAVIER</t>
+          <t>C000875691 - PUJAICO RUIZ DE FERNANDEZ ANGELA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>S17736445</t>
+          <t>S17742299</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3861,7 +3861,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>80410</v>
+        <v>12277</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -3895,12 +3895,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>C004218242</t>
+          <t>C001161300</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>C004218242 - JHONG RAFFO CRISTIABEL</t>
+          <t>C001161300 - RIVERA GOMEZ ANGEL RENE</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3920,11 +3920,11 @@
         <v>46235</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>46247</v>
+        <v>46242</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>S17838631</t>
+          <t>S17724116</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3947,7 +3947,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3977,7 +3977,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>69615</v>
+        <v>31604</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -4011,12 +4011,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>C001761926</t>
+          <t>C001538483</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>C001761926 - ESPINOZA CHOQUE SUSANA ARACELI</t>
+          <t>C001538483 - DE LA ROSA AZURZA REYNA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4036,11 +4036,11 @@
         <v>46235</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>46242</v>
+        <v>46244</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>S17725411</t>
+          <t>S17740567</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4063,7 +4063,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -4093,7 +4093,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>69954</v>
+        <v>12275</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -4127,12 +4127,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>C004244157</t>
+          <t>C001198026</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>C004244157 - PEÑA ANCHANTE EVELYN ALEJANDRA</t>
+          <t>C001198026 -  VARGAS ANCCANA KELLY JUDITH</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4152,11 +4152,11 @@
         <v>46235</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>46245</v>
+        <v>46241</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>S17794291</t>
+          <t>S17679924</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4209,7 +4209,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>96420</v>
+        <v>48663</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -4243,12 +4243,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>C001693960</t>
+          <t>C001539717</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>C001693960 - FERNANDEZ CALDERON SOLARI LILY</t>
+          <t>C001539717 - QUISPE QUIHUE ABIGAIL NANCY</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4268,11 +4268,11 @@
         <v>46235</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>46244</v>
+        <v>46242</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>S17741332</t>
+          <t>S17721236</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4325,7 +4325,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>93955</v>
+        <v>42668</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -4359,12 +4359,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>C004243794</t>
+          <t>C001683409</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>C004243794 - DELGADO PALOMINO ELSA MARIA</t>
+          <t>C001683409 - MEDRANO SAAVEDRA YANINA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4384,11 +4384,11 @@
         <v>46235</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>46247</v>
+        <v>46241</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>S17846292</t>
+          <t>S17696189</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4411,7 +4411,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>Quiere comparar precios antes de comprar</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4441,7 +4441,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>48663</v>
+        <v>69954</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -4475,12 +4475,12 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>C001539717</t>
+          <t>C004244157</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>C001539717 - QUISPE QUIHUE ABIGAIL NANCY</t>
+          <t>C004244157 - PEÑA ANCHANTE EVELYN ALEJANDRA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4500,11 +4500,11 @@
         <v>46235</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>46242</v>
+        <v>46245</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>S17721236</t>
+          <t>S17794291</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4557,7 +4557,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>42668</v>
+        <v>93955</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -4591,12 +4591,12 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>C001683409</t>
+          <t>C004243794</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>C001683409 - MEDRANO SAAVEDRA YANINA</t>
+          <t>C004243794 - DELGADO PALOMINO ELSA MARIA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4616,11 +4616,11 @@
         <v>46235</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>46241</v>
+        <v>46247</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>S17696189</t>
+          <t>S17846292</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4643,7 +4643,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Quiere comparar precios antes de comprar</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4673,7 +4673,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>12275</v>
+        <v>96420</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -4707,12 +4707,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>C001198026</t>
+          <t>C001693960</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>C001198026 -  VARGAS ANCCANA KELLY JUDITH</t>
+          <t>C001693960 - FERNANDEZ CALDERON SOLARI LILY</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4732,11 +4732,11 @@
         <v>46235</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>S17679924</t>
+          <t>S17741332</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4759,7 +4759,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4789,7 +4789,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>12541</v>
+        <v>98274</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -4823,12 +4823,12 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>C000881499</t>
+          <t>C004178774</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>C000881499 - PALLIN QUISPE HAYDEE MARTINA</t>
+          <t>C004178774 - ESPINOZA QUIJANDRIA CARLOS MARTIN</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>S17675946</t>
+          <t>S17671616</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>Quiere comparar precios antes de comprar</t>
+          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4905,7 +4905,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>7128</v>
+        <v>92571</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -4939,12 +4939,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>C001013079</t>
+          <t>C004203037</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>C001013079 - SULCA HUACHUA MIGUEL ARTURO</t>
+          <t>C004203037 - DIAZ CHUQUIHUACCHA FLOR LILIANA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>S17657573</t>
+          <t>S17649592</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -5021,7 +5021,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>64774</v>
+        <v>69254</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>C004059422</t>
+          <t>C004171458</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>C004059422 - MORALES HERRERA MATEA EVANGELINA</t>
+          <t>C004171458 - AQUINO AHON PAULA NAOMI</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5084,7 +5084,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>S17850764</t>
+          <t>S17852237</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5130,14 +5130,14 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más productos disponibles</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>64671</v>
+        <v>64774</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -5171,12 +5171,12 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>C004044936</t>
+          <t>C004059422</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>C004044936 - HUAYANCA CASTILLO LIBIA GISELLA</t>
+          <t>C004059422 - MORALES HERRERA MATEA EVANGELINA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5200,7 +5200,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>S17852663</t>
+          <t>S17850764</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5223,7 +5223,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -5253,7 +5253,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>54741</v>
+        <v>64671</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>C001749448</t>
+          <t>C004044936</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>C001749448 - ROJAS DE LA CRUZ INGRID JANET</t>
+          <t>C004044936 - HUAYANCA CASTILLO LIBIA GISELLA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5312,11 +5312,11 @@
         <v>46235</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>46240</v>
+        <v>46247</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>S17665970</t>
+          <t>S17852663</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5339,7 +5339,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>Quiere comparar precios antes de comprar</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -5369,7 +5369,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>98274</v>
+        <v>54741</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -5403,12 +5403,12 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>C004178774</t>
+          <t>C001749448</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>C004178774 - ESPINOZA QUIJANDRIA CARLOS MARTIN</t>
+          <t>C001749448 - ROJAS DE LA CRUZ INGRID JANET</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5432,7 +5432,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>S17671616</t>
+          <t>S17665970</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5455,7 +5455,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
+          <t>Quiere comparar precios antes de comprar</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5485,7 +5485,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>92571</v>
+        <v>12541</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -5519,12 +5519,12 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>C004203037</t>
+          <t>C000881499</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>C004203037 - DIAZ CHUQUIHUACCHA FLOR LILIANA</t>
+          <t>C000881499 - PALLIN QUISPE HAYDEE MARTINA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5548,7 +5548,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>S17649592</t>
+          <t>S17675946</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+          <t>Quiere comparar precios antes de comprar</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5601,7 +5601,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>69254</v>
+        <v>7128</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -5635,12 +5635,12 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>C004171458</t>
+          <t>C001013079</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>C004171458 - AQUINO AHON PAULA NAOMI</t>
+          <t>C001013079 - SULCA HUACHUA MIGUEL ARTURO</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5660,11 +5660,11 @@
         <v>46235</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>46247</v>
+        <v>46240</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>S17852237</t>
+          <t>S17657573</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5687,7 +5687,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5710,14 +5710,14 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>Más productos disponibles</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>72146</v>
+        <v>5984</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -5751,12 +5751,12 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>C004180314</t>
+          <t>C000875215</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>C004180314 - CONTRERAS MENDOZA ALAN BLADE</t>
+          <t>C000875215 - QUISPE ATOCCSA CARMEN FAUSTINA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5780,7 +5780,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>S17596870</t>
+          <t>S17586382</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5833,7 +5833,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>93147</v>
+        <v>4893</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -5867,12 +5867,12 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>C004025529</t>
+          <t>C000882553</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>C004025529 - EL BATAN DEL NORTE E.I.R.L.</t>
+          <t>C000882553 - ECHEVARRIA ALFARO SOFIA LUISA</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5896,7 +5896,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>S17596445</t>
+          <t>S17581951</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5919,7 +5919,7 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5949,7 +5949,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>97167</v>
+        <v>10166</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>C001563658</t>
+          <t>C000877090</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>C001563658 - DE LA CRUZ MORALES DE ALVITES DINA MARGA</t>
+          <t>C000877090 - UCULMANA ANICAMA PILAR</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6012,7 +6012,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>S17598854</t>
+          <t>S17606945</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6035,7 +6035,7 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -6065,7 +6065,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>106138</v>
+        <v>45676</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>C000883040</t>
+          <t>C001748378</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>C000883040 - YALLE CASAVILCA NELIO</t>
+          <t>C001748378 - FARFAN CHILON FATIMA SARITA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6128,7 +6128,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>S17584535</t>
+          <t>S17584263</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -6181,7 +6181,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>108588</v>
+        <v>54119</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -6215,12 +6215,12 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>C000875926</t>
+          <t>C001748916</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>C000875926 - QUISPE CACERES DORIS</t>
+          <t>C001748916 - CUSQUISIBAN QUISPE MARIA MARCELINA</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6240,11 +6240,11 @@
         <v>46235</v>
       </c>
       <c r="N50" s="3" t="n">
-        <v>46240</v>
+        <v>46238</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>S17671001</t>
+          <t>S17584197</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6267,7 +6267,7 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+          <t>Prefiere negociar con el vendedor</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -6297,7 +6297,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>45676</v>
+        <v>72146</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -6331,12 +6331,12 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>C001748378</t>
+          <t>C004180314</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>C001748378 - FARFAN CHILON FATIMA SARITA</t>
+          <t>C004180314 - CONTRERAS MENDOZA ALAN BLADE</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6360,7 +6360,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>S17584263</t>
+          <t>S17596870</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6383,7 +6383,7 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -6413,7 +6413,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>54119</v>
+        <v>97167</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -6447,12 +6447,12 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>C001748916</t>
+          <t>C001563658</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>C001748916 - CUSQUISIBAN QUISPE MARIA MARCELINA</t>
+          <t>C001563658 - DE LA CRUZ MORALES DE ALVITES DINA MARGA</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>S17584197</t>
+          <t>S17598854</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6499,7 +6499,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>Prefiere negociar con el vendedor</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -6529,7 +6529,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>5984</v>
+        <v>93147</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -6563,12 +6563,12 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>C000875215</t>
+          <t>C004025529</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>C000875215 - QUISPE ATOCCSA CARMEN FAUSTINA</t>
+          <t>C004025529 - EL BATAN DEL NORTE E.I.R.L.</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6592,7 +6592,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>S17586382</t>
+          <t>S17596445</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6615,7 +6615,7 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6645,7 +6645,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>4893</v>
+        <v>106138</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -6679,12 +6679,12 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>C000882553</t>
+          <t>C000883040</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>C000882553 - ECHEVARRIA ALFARO SOFIA LUISA</t>
+          <t>C000883040 - YALLE CASAVILCA NELIO</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>S17581951</t>
+          <t>S17584535</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6761,7 +6761,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>10166</v>
+        <v>108588</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -6795,12 +6795,12 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>C000877090</t>
+          <t>C000875926</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>C000877090 - UCULMANA ANICAMA PILAR</t>
+          <t>C000875926 - QUISPE CACERES DORIS</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6820,11 +6820,11 @@
         <v>46235</v>
       </c>
       <c r="N55" s="3" t="n">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>S17606945</t>
+          <t>S17671001</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6847,7 +6847,7 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6877,7 +6877,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>17428</v>
+        <v>97694</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -6911,12 +6911,12 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>C001284711</t>
+          <t>C001683408</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>C001284711 - ANDRES PARIONA IDALIA MAXIMA</t>
+          <t>C001683408 - URIBE GUILLEN GREGORIO HUMBERTO</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6936,11 +6936,11 @@
         <v>46235</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>46240</v>
+        <v>46237</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>S17663221</t>
+          <t>S17564753</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6963,7 +6963,7 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6993,7 +6993,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>2927</v>
+        <v>96925</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -7027,12 +7027,12 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>C000881830</t>
+          <t>C004239540</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>C000881830 - AROSTIGUE DE COLLADO FELICITA</t>
+          <t>C004239540 - MARCATINCO SOTELO NESTOR RICHARD</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -7052,11 +7052,11 @@
         <v>46235</v>
       </c>
       <c r="N57" s="3" t="n">
-        <v>46240</v>
+        <v>46246</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>S17671949</t>
+          <t>S17829277</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -7079,7 +7079,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -7109,7 +7109,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>30854</v>
+        <v>89076</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -7143,12 +7143,12 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>C001506102</t>
+          <t>C001547860</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>C001506102 - QUICHUA ARROYO MARILU</t>
+          <t>C001547860 - TORRES PAREDES ORCELINDA MIRELLA</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -7172,7 +7172,7 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>S17572956</t>
+          <t>S17576599</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -7225,7 +7225,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>52001</v>
+        <v>78486</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -7259,12 +7259,12 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>C001709978</t>
+          <t>C004243810</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>C001709978 - QUISPE NEYRA BEATRIZ LILIANA</t>
+          <t>C004243810 - ORE CURI CARMEN JENNIFER</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -7284,11 +7284,11 @@
         <v>46235</v>
       </c>
       <c r="N59" s="3" t="n">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>S17565887</t>
+          <t>S17666877</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -7311,7 +7311,7 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -7341,7 +7341,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>42754</v>
+        <v>67722</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>C001722065</t>
+          <t>C004191304</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>C001722065 - PACHECO AQUIJE GABRIELA CECILIA</t>
+          <t>C004191304 - SARAVIA TORRES HECTOR LUIS</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -7400,11 +7400,11 @@
         <v>46235</v>
       </c>
       <c r="N60" s="3" t="n">
-        <v>46237</v>
+        <v>46243</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>S17566776</t>
+          <t>S17733691</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -7427,7 +7427,7 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -7435,11 +7435,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="V60" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
+      <c r="V60" t="inlineStr"/>
       <c r="W60" t="inlineStr"/>
       <c r="X60" t="inlineStr"/>
       <c r="Y60" t="inlineStr">
@@ -7461,7 +7457,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>41751</v>
+        <v>52001</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -7495,12 +7491,12 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>C001615633</t>
+          <t>C001709978</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>C001615633 - GARCIA CORDOVA JUANA ELIANA</t>
+          <t>C001709978 - QUISPE NEYRA BEATRIZ LILIANA</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -7524,7 +7520,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>S17568791</t>
+          <t>S17565887</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -7570,14 +7566,14 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>Más productos disponibles</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>96925</v>
+        <v>42754</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -7611,12 +7607,12 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>C004239540</t>
+          <t>C001722065</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>C004239540 - MARCATINCO SOTELO NESTOR RICHARD</t>
+          <t>C001722065 - PACHECO AQUIJE GABRIELA CECILIA</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -7636,11 +7632,11 @@
         <v>46235</v>
       </c>
       <c r="N62" s="3" t="n">
-        <v>46246</v>
+        <v>46237</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>S17829277</t>
+          <t>S17566776</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -7663,7 +7659,7 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -7671,7 +7667,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="V62" t="inlineStr"/>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
       <c r="W62" t="inlineStr"/>
       <c r="X62" t="inlineStr"/>
       <c r="Y62" t="inlineStr">
@@ -7693,7 +7693,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>97694</v>
+        <v>41751</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -7727,12 +7727,12 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>C001683408</t>
+          <t>C001615633</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>C001683408 - URIBE GUILLEN GREGORIO HUMBERTO</t>
+          <t>C001615633 - GARCIA CORDOVA JUANA ELIANA</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -7756,7 +7756,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>S17564753</t>
+          <t>S17568791</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -7802,14 +7802,14 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más productos disponibles</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>89076</v>
+        <v>17428</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -7843,12 +7843,12 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>C001547860</t>
+          <t>C001284711</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>C001547860 - TORRES PAREDES ORCELINDA MIRELLA</t>
+          <t>C001284711 - ANDRES PARIONA IDALIA MAXIMA</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -7868,11 +7868,11 @@
         <v>46235</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>S17576599</t>
+          <t>S17663221</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -7895,7 +7895,7 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -7925,7 +7925,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>78486</v>
+        <v>2927</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -7959,12 +7959,12 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>C004243810</t>
+          <t>C000881830</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>C004243810 - ORE CURI CARMEN JENNIFER</t>
+          <t>C000881830 - AROSTIGUE DE COLLADO FELICITA</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -7988,7 +7988,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>S17666877</t>
+          <t>S17671949</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -8041,7 +8041,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>67722</v>
+        <v>30854</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -8075,12 +8075,12 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>C004191304</t>
+          <t>C001506102</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>C004191304 - SARAVIA TORRES HECTOR LUIS</t>
+          <t>C001506102 - QUICHUA ARROYO MARILU</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -8100,11 +8100,11 @@
         <v>46235</v>
       </c>
       <c r="N66" s="3" t="n">
-        <v>46243</v>
+        <v>46237</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>S17733691</t>
+          <t>S17572956</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -8127,7 +8127,7 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -8157,7 +8157,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>71751</v>
+        <v>1830</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>C001712478</t>
+          <t>C000882632</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>C001712478 - BENDEZU FERREYRA NER AMILCAR</t>
+          <t>C000882632 - RAMIREZ VICU A JULIA</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -8216,11 +8216,11 @@
         <v>46235</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>46247</v>
+        <v>46235</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>S17837288</t>
+          <t>S17535740</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -8243,7 +8243,7 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -8273,7 +8273,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>80583</v>
+        <v>17543</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -8307,12 +8307,12 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>C004205639</t>
+          <t>C001390551</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>C004205639 - NIEVES OQUEÑA LILIANA</t>
+          <t>C001390551 - ALEJO QUISPE EDITH VILMA</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -8332,11 +8332,11 @@
         <v>46235</v>
       </c>
       <c r="N68" s="3" t="n">
-        <v>46244</v>
+        <v>46235</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>S17756161</t>
+          <t>S17540777</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -8359,7 +8359,7 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -8389,7 +8389,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>96923</v>
+        <v>10855</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>C004189020</t>
+          <t>C001158988</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>C004189020 - HUAMAN VARGAS ENMA</t>
+          <t>C001158988 - ECHACCAYA CUCHO JESUS ALBERTO</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -8452,7 +8452,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>S17664477</t>
+          <t>S17665048</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -8505,7 +8505,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>111544</v>
+        <v>71751</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -8539,12 +8539,12 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>C000872477</t>
+          <t>C001712478</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>C000872477 - CHANCA BELLIDO LEONIDAS</t>
+          <t>C001712478 - BENDEZU FERREYRA NER AMILCAR</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -8564,11 +8564,11 @@
         <v>46235</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>46240</v>
+        <v>46247</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>S17660355</t>
+          <t>S17837288</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -8621,7 +8621,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>1830</v>
+        <v>80583</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -8655,12 +8655,12 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>C000882632</t>
+          <t>C004205639</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>C000882632 - RAMIREZ VICU A JULIA</t>
+          <t>C004205639 - NIEVES OQUEÑA LILIANA</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -8680,11 +8680,11 @@
         <v>46235</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>46235</v>
+        <v>46244</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>S17535740</t>
+          <t>S17756161</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -8707,7 +8707,7 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -8737,7 +8737,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>17543</v>
+        <v>96923</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -8771,12 +8771,12 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>C001390551</t>
+          <t>C004189020</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>C001390551 - ALEJO QUISPE EDITH VILMA</t>
+          <t>C004189020 - HUAMAN VARGAS ENMA</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -8796,11 +8796,11 @@
         <v>46235</v>
       </c>
       <c r="N72" s="3" t="n">
-        <v>46235</v>
+        <v>46240</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>S17540777</t>
+          <t>S17664477</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -8823,7 +8823,7 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -8853,7 +8853,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>10855</v>
+        <v>111544</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -8887,12 +8887,12 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>C001158988</t>
+          <t>C000872477</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>C001158988 - ECHACCAYA CUCHO JESUS ALBERTO</t>
+          <t>C000872477 - CHANCA BELLIDO LEONIDAS</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -8916,7 +8916,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>S17665048</t>
+          <t>S17660355</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
